--- a/台北畫家管理費資訊-20241102.xlsx
+++ b/台北畫家管理費資訊-20241102.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">門牌!$I$1:$I$35</definedName>
   </definedNames>
-  <calcPr calcId="125725" iterate="1"/>
+  <calcPr calcId="125725"/>
 </workbook>
 </file>
 
@@ -160,9 +160,6 @@
     <t>呂紹賢</t>
   </si>
   <si>
-    <t>許文鐘</t>
-  </si>
-  <si>
     <t>胡警隆</t>
   </si>
   <si>
@@ -869,6 +866,10 @@
   </si>
   <si>
     <t>六福路247巷1號三樓</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>許文鍾</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1417,7 +1418,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:J35"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -1432,34 +1432,34 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="C1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>110</v>
-      </c>
       <c r="I1" s="32" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" hidden="1">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -1467,7 +1467,7 @@
         <v>34</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
@@ -1486,7 +1486,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="3" spans="1:10" hidden="1">
+    <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1494,7 +1494,7 @@
         <v>35</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>36</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D4" s="4">
         <v>1</v>
@@ -1540,13 +1540,13 @@
         <v>550</v>
       </c>
       <c r="I4" t="s">
+        <v>219</v>
+      </c>
+      <c r="J4" t="s">
         <v>220</v>
       </c>
-      <c r="J4" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" hidden="1">
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -1554,7 +1554,7 @@
         <v>37</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -1578,10 +1578,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D6" s="4">
         <v>1</v>
@@ -1600,13 +1600,13 @@
         <v>550</v>
       </c>
       <c r="I6" t="s">
+        <v>219</v>
+      </c>
+      <c r="J6" t="s">
         <v>220</v>
       </c>
-      <c r="J6" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" hidden="1">
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -1614,7 +1614,7 @@
         <v>38</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
@@ -1641,7 +1641,7 @@
         <v>39</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D8" s="4">
         <v>1</v>
@@ -1660,13 +1660,13 @@
         <v>650</v>
       </c>
       <c r="I8" t="s">
+        <v>219</v>
+      </c>
+      <c r="J8" t="s">
         <v>220</v>
       </c>
-      <c r="J8" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" hidden="1">
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>40</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D9" s="2">
         <v>1</v>
@@ -1693,7 +1693,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1">
+    <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
@@ -1701,7 +1701,7 @@
         <v>41</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -1720,7 +1720,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1">
+    <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -1728,7 +1728,7 @@
         <v>42</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
@@ -1755,7 +1755,7 @@
         <v>43</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -1774,13 +1774,13 @@
         <v>500</v>
       </c>
       <c r="I12" t="s">
+        <v>219</v>
+      </c>
+      <c r="J12" t="s">
         <v>220</v>
       </c>
-      <c r="J12" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" hidden="1">
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>44</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D13" s="2">
         <v>1</v>
@@ -1807,7 +1807,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="14" spans="1:10" hidden="1">
+    <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>45</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D14" s="4">
         <v>1</v>
@@ -1839,10 +1839,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>46</v>
+        <v>235</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -1861,21 +1861,21 @@
         <v>550</v>
       </c>
       <c r="I15" t="s">
+        <v>219</v>
+      </c>
+      <c r="J15" t="s">
         <v>220</v>
       </c>
-      <c r="J15" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" hidden="1">
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D16" s="4">
         <v>1</v>
@@ -1896,13 +1896,13 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D17" s="2">
         <v>1</v>
@@ -1921,18 +1921,18 @@
         <v>500</v>
       </c>
       <c r="I17" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" hidden="1">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D18" s="4">
         <v>1</v>
@@ -1951,15 +1951,15 @@
         <v>500</v>
       </c>
     </row>
-    <row r="19" spans="1:10" hidden="1">
+    <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D19" s="2">
         <v>1</v>
@@ -1983,10 +1983,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D20" s="4">
         <v>1</v>
@@ -2005,21 +2005,21 @@
         <v>650</v>
       </c>
       <c r="I20" t="s">
+        <v>219</v>
+      </c>
+      <c r="J20" t="s">
         <v>220</v>
       </c>
-      <c r="J20" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" hidden="1">
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D21" s="2">
         <v>1</v>
@@ -2038,15 +2038,15 @@
         <v>650</v>
       </c>
     </row>
-    <row r="22" spans="1:10" hidden="1">
+    <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D22" s="4">
         <v>1</v>
@@ -2065,15 +2065,15 @@
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="1:10" hidden="1">
+    <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D23" s="2">
         <v>1</v>
@@ -2097,10 +2097,10 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D24" s="4">
         <v>1</v>
@@ -2119,18 +2119,18 @@
         <v>500</v>
       </c>
       <c r="I24" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" hidden="1">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D25" s="2">
         <v>1</v>
@@ -2154,10 +2154,10 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D26" s="4">
         <v>1</v>
@@ -2176,10 +2176,10 @@
         <v>500</v>
       </c>
       <c r="I26" t="s">
+        <v>219</v>
+      </c>
+      <c r="J26" t="s">
         <v>220</v>
-      </c>
-      <c r="J26" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -2187,10 +2187,10 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D27" s="2">
         <v>1</v>
@@ -2209,21 +2209,21 @@
         <v>650</v>
       </c>
       <c r="I27" t="s">
+        <v>219</v>
+      </c>
+      <c r="J27" t="s">
         <v>220</v>
       </c>
-      <c r="J27" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" hidden="1">
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D28" s="4">
         <v>1</v>
@@ -2242,15 +2242,15 @@
         <v>500</v>
       </c>
     </row>
-    <row r="29" spans="1:10" hidden="1">
+    <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D29" s="2">
         <v>1</v>
@@ -2269,15 +2269,15 @@
         <v>500</v>
       </c>
     </row>
-    <row r="30" spans="1:10" hidden="1">
+    <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D30" s="4">
         <v>1</v>
@@ -2301,10 +2301,10 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D31" s="2">
         <v>1</v>
@@ -2323,21 +2323,21 @@
         <v>600</v>
       </c>
       <c r="I31" t="s">
+        <v>219</v>
+      </c>
+      <c r="J31" t="s">
         <v>220</v>
       </c>
-      <c r="J31" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" hidden="1">
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D32" s="4">
         <v>1</v>
@@ -2356,15 +2356,15 @@
         <v>500</v>
       </c>
     </row>
-    <row r="33" spans="1:10" hidden="1">
+    <row r="33" spans="1:10">
       <c r="A33" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D33" s="2">
         <v>1</v>
@@ -2388,10 +2388,10 @@
         <v>32</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D34" s="4">
         <v>1</v>
@@ -2410,10 +2410,10 @@
         <v>650</v>
       </c>
       <c r="I34" t="s">
+        <v>219</v>
+      </c>
+      <c r="J34" t="s">
         <v>220</v>
-      </c>
-      <c r="J34" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -2421,10 +2421,10 @@
         <v>33</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D35" s="2">
         <v>1</v>
@@ -2443,19 +2443,15 @@
         <v>500</v>
       </c>
       <c r="I35" t="s">
+        <v>219</v>
+      </c>
+      <c r="J35" t="s">
         <v>220</v>
-      </c>
-      <c r="J35" t="s">
-        <v>221</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="I1:I35">
-    <filterColumn colId="0">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
+    <filterColumn colId="0"/>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2474,16 +2470,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B1" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="D1" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2491,13 +2487,13 @@
         <v>27</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C2" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="D2" s="18" t="s">
         <v>131</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2505,13 +2501,13 @@
         <v>28</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C3" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="D3" s="18" t="s">
         <v>131</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2519,13 +2515,13 @@
         <v>27</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2533,13 +2529,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -2562,31 +2558,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C1" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="E1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="H1" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>115</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2595,10 +2591,10 @@
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E2" s="6">
         <v>1</v>
@@ -2607,7 +2603,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H2" s="11">
         <f>DATEDIF(C2,D2,"m")+1</f>
@@ -2624,10 +2620,10 @@
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E3" s="6">
         <v>0</v>
@@ -2636,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H3" s="11">
         <f t="shared" ref="H3:H37" si="0">DATEDIF(C3,D3,"m")+1</f>
@@ -2653,10 +2649,10 @@
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E4" s="6">
         <v>0</v>
@@ -2665,7 +2661,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H4" s="11">
         <f t="shared" si="0"/>
@@ -2682,10 +2678,10 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E5" s="6">
         <v>0</v>
@@ -2694,7 +2690,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H5" s="11">
         <f t="shared" si="0"/>
@@ -2711,10 +2707,10 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E6" s="6">
         <v>0</v>
@@ -2723,7 +2719,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H6" s="11">
         <f t="shared" si="0"/>
@@ -2740,10 +2736,10 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E7" s="6">
         <v>1</v>
@@ -2752,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H7" s="11">
         <f t="shared" si="0"/>
@@ -2769,10 +2765,10 @@
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E8" s="6">
         <v>1</v>
@@ -2781,7 +2777,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H8" s="11">
         <f t="shared" si="0"/>
@@ -2798,10 +2794,10 @@
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E9" s="6">
         <v>1</v>
@@ -2810,7 +2806,7 @@
         <v>2</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H9" s="11">
         <f t="shared" si="0"/>
@@ -2827,10 +2823,10 @@
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E10" s="6">
         <v>1</v>
@@ -2839,7 +2835,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H10" s="11">
         <f t="shared" si="0"/>
@@ -2856,10 +2852,10 @@
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E11" s="6">
         <v>0</v>
@@ -2868,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H11" s="11">
         <f t="shared" si="0"/>
@@ -2885,10 +2881,10 @@
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E12" s="6">
         <v>0</v>
@@ -2897,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H12" s="11">
         <f t="shared" si="0"/>
@@ -2914,10 +2910,10 @@
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E13" s="8">
         <v>0</v>
@@ -2926,7 +2922,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H13" s="11">
         <f t="shared" si="0"/>
@@ -2943,10 +2939,10 @@
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E14" s="6">
         <v>0</v>
@@ -2955,7 +2951,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H14" s="11">
         <f t="shared" si="0"/>
@@ -2972,10 +2968,10 @@
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E15" s="6">
         <v>0</v>
@@ -2984,7 +2980,7 @@
         <v>1</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H15" s="11">
         <f t="shared" si="0"/>
@@ -3001,10 +2997,10 @@
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E16" s="6">
         <v>1</v>
@@ -3013,7 +3009,7 @@
         <v>1</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H16" s="11">
         <f t="shared" si="0"/>
@@ -3030,10 +3026,10 @@
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E17" s="6">
         <v>0</v>
@@ -3042,7 +3038,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H17" s="11">
         <f t="shared" si="0"/>
@@ -3059,10 +3055,10 @@
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E18" s="6">
         <v>0</v>
@@ -3071,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H18" s="11">
         <f t="shared" si="0"/>
@@ -3088,10 +3084,10 @@
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E19" s="9">
         <v>1</v>
@@ -3100,7 +3096,7 @@
         <v>1</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H19" s="11">
         <f t="shared" si="0"/>
@@ -3117,10 +3113,10 @@
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E20" s="6">
         <v>1</v>
@@ -3129,7 +3125,7 @@
         <v>2</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H20" s="11">
         <f t="shared" si="0"/>
@@ -3146,10 +3142,10 @@
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E21" s="10">
         <v>0</v>
@@ -3158,7 +3154,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H21" s="11">
         <f t="shared" si="0"/>
@@ -3175,10 +3171,10 @@
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E22" s="6">
         <v>0</v>
@@ -3187,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H22" s="11">
         <f t="shared" si="0"/>
@@ -3204,10 +3200,10 @@
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E23" s="6">
         <v>0</v>
@@ -3216,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H23" s="11">
         <f t="shared" si="0"/>
@@ -3233,10 +3229,10 @@
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E24" s="6">
         <v>0</v>
@@ -3245,7 +3241,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H24" s="11">
         <f t="shared" si="0"/>
@@ -3262,10 +3258,10 @@
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E25" s="6">
         <v>1</v>
@@ -3274,7 +3270,7 @@
         <v>1</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H25" s="11">
         <f t="shared" si="0"/>
@@ -3291,10 +3287,10 @@
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E26" s="6">
         <v>0</v>
@@ -3303,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H26" s="11">
         <f t="shared" si="0"/>
@@ -3319,13 +3315,13 @@
         <v>27</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E27" s="29">
         <v>0</v>
@@ -3334,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H27" s="30">
         <f t="shared" ref="H27:H28" si="2">DATEDIF(C27,D27,"m")+1</f>
@@ -3350,13 +3346,13 @@
         <v>28</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E28" s="29">
         <v>0</v>
@@ -3365,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H28" s="30">
         <f t="shared" si="2"/>
@@ -3382,10 +3378,10 @@
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E29" s="6">
         <v>1</v>
@@ -3394,7 +3390,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H29" s="11">
         <f t="shared" si="0"/>
@@ -3407,14 +3403,14 @@
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E30" s="6">
         <v>0</v>
@@ -3423,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H30" s="11">
         <f t="shared" si="0"/>
@@ -3440,10 +3436,10 @@
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E31" s="6">
         <v>1</v>
@@ -3452,7 +3448,7 @@
         <v>2</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H31" s="11">
         <f t="shared" si="0"/>
@@ -3469,10 +3465,10 @@
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E32" s="6">
         <v>1</v>
@@ -3481,7 +3477,7 @@
         <v>1</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H32" s="11">
         <f t="shared" si="0"/>
@@ -3498,10 +3494,10 @@
       </c>
       <c r="B33" s="12"/>
       <c r="C33" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E33" s="13">
         <v>0</v>
@@ -3510,7 +3506,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H33" s="11">
         <f t="shared" si="0"/>
@@ -3523,25 +3519,25 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="19" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D34" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="E34" s="21">
+        <v>0</v>
+      </c>
+      <c r="F34" s="21">
+        <v>0</v>
+      </c>
+      <c r="G34" s="22" t="s">
         <v>125</v>
-      </c>
-      <c r="E34" s="21">
-        <v>0</v>
-      </c>
-      <c r="F34" s="21">
-        <v>0</v>
-      </c>
-      <c r="G34" s="22" t="s">
-        <v>126</v>
       </c>
       <c r="H34" s="20">
         <f>DATEDIF(C34,D34,"m")+1</f>
@@ -3557,22 +3553,22 @@
         <v>28</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D35" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="E35" s="21">
+        <v>0</v>
+      </c>
+      <c r="F35" s="21">
+        <v>0</v>
+      </c>
+      <c r="G35" s="22" t="s">
         <v>125</v>
-      </c>
-      <c r="E35" s="21">
-        <v>0</v>
-      </c>
-      <c r="F35" s="21">
-        <v>0</v>
-      </c>
-      <c r="G35" s="22" t="s">
-        <v>126</v>
       </c>
       <c r="H35" s="20">
         <f>DATEDIF(C35,D35,"m")+1</f>
@@ -3588,13 +3584,13 @@
         <v>27</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D36" s="25" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E36" s="26">
         <v>0</v>
@@ -3603,7 +3599,7 @@
         <v>1</v>
       </c>
       <c r="G36" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H36" s="20">
         <f t="shared" si="0"/>
@@ -3619,13 +3615,13 @@
         <v>28</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D37" s="25" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E37" s="26">
         <v>0</v>
@@ -3634,7 +3630,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H37" s="20">
         <f t="shared" si="0"/>
@@ -3650,13 +3646,13 @@
         <v>27</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C38" s="25" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D38" s="25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E38" s="26">
         <v>0</v>
@@ -3665,7 +3661,7 @@
         <v>1</v>
       </c>
       <c r="G38" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H38" s="20">
         <f t="shared" ref="H38:H39" si="4">DATEDIF(C38,D38,"m")+1</f>
@@ -3681,13 +3677,13 @@
         <v>28</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C39" s="25" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D39" s="25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E39" s="26">
         <v>0</v>
@@ -3696,7 +3692,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H39" s="20">
         <f t="shared" si="4"/>
@@ -3725,972 +3721,972 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="E1" t="s">
         <v>137</v>
-      </c>
-      <c r="E1" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D2" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="E2" t="s">
         <v>225</v>
-      </c>
-      <c r="E2" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E5" t="s">
         <v>150</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E5" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D13" s="27" t="s">
         <v>163</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="E13" t="s">
         <v>142</v>
-      </c>
-      <c r="D13" s="27" t="s">
-        <v>164</v>
-      </c>
-      <c r="E13" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="E14" t="s">
         <v>142</v>
-      </c>
-      <c r="D14" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="E14" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E16" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D20" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="E20" t="s">
         <v>142</v>
-      </c>
-      <c r="D20" s="27" t="s">
-        <v>170</v>
-      </c>
-      <c r="E20" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D21" s="27">
         <v>20</v>
       </c>
       <c r="E21" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="E22" t="s">
         <v>142</v>
-      </c>
-      <c r="D22" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="E22" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E23" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F23" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E26" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E27" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D28" s="27" t="s">
         <v>207</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D28" s="27" t="s">
-        <v>208</v>
-      </c>
       <c r="E28" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E29" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E31" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C32" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D32" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="E32" t="s">
         <v>142</v>
-      </c>
-      <c r="D32" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="E32" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D33" s="27" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E33" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E34" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E35" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E36" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E37" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C38" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="E38" t="s">
+        <v>150</v>
+      </c>
+      <c r="F38" t="s">
         <v>204</v>
-      </c>
-      <c r="E38" t="s">
-        <v>151</v>
-      </c>
-      <c r="F38" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E39" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E40" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E41" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F41" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E43" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C45" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D45" s="27" t="s">
+        <v>177</v>
+      </c>
+      <c r="E45" t="s">
         <v>142</v>
-      </c>
-      <c r="D45" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="E45" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D46" s="27" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E46" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E47" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E48" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E50" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E51" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E52" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E53" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E54" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E55" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E58" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E59" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B60" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D60" s="27" t="s">
         <v>188</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="E60" t="s">
         <v>142</v>
-      </c>
-      <c r="D60" s="27" t="s">
-        <v>189</v>
-      </c>
-      <c r="E60" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E61" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E62" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E65" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E66" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E67" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E68" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E69" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C70" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D70" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="E70" t="s">
         <v>142</v>
-      </c>
-      <c r="D70" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="E70" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B71" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D71" s="27" t="s">
         <v>222</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="E71" t="s">
         <v>142</v>
-      </c>
-      <c r="D71" s="27" t="s">
-        <v>223</v>
-      </c>
-      <c r="E71" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E72" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
